--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/4735-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/4735-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9134E65E-8CA7-42C0-8466-42CB43DDB1D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{12E3ECDD-A4A3-404A-9309-6B5737A96F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{CF84B194-A8F4-44ED-8143-58C7283E8744}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{C4A71AAE-B8AF-4C86-B6D9-3E7CB765F4EF}"/>
   </bookViews>
   <sheets>
     <sheet name="4735-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1544,23 +1544,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3509F8B4-5834-4DDD-8A93-D84D02EB0F52}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{133311D2-DE4E-401C-813C-3D8A5092F99F}">
   <dimension ref="A1:R44"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="18" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1588,7 +1587,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1618,7 +1617,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1664,7 +1663,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1714,7 +1713,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1768,7 +1767,7 @@
         <v>7.12</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1824,7 +1823,7 @@
         <v>2.04</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1880,7 +1879,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>25</v>
       </c>
@@ -1936,7 +1935,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>25</v>
       </c>
@@ -1992,7 +1991,7 @@
         <v>2.86</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="39">
         <v>2024</v>
       </c>
@@ -2046,7 +2045,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
@@ -2102,7 +2101,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
@@ -2158,7 +2157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>25</v>
       </c>
@@ -2214,7 +2213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>25</v>
       </c>
@@ -2270,7 +2269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="37">
         <v>2023</v>
       </c>
@@ -2324,7 +2323,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>25</v>
       </c>
@@ -2380,7 +2379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
@@ -2436,7 +2435,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2492,7 +2491,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2548,7 +2547,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2022</v>
       </c>
@@ -2602,7 +2601,7 @@
         <v>5.97</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
@@ -2658,7 +2657,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2714,7 +2713,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>25</v>
       </c>
@@ -2770,7 +2769,7 @@
         <v>1.29</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>25</v>
       </c>
@@ -2826,7 +2825,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>2021</v>
       </c>
@@ -2880,7 +2879,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>25</v>
       </c>
@@ -2936,7 +2935,7 @@
         <v>2.04</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>25</v>
       </c>
@@ -2992,7 +2991,7 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>25</v>
       </c>
@@ -3048,7 +3047,7 @@
         <v>1.96</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>25</v>
       </c>
@@ -3104,7 +3103,7 @@
         <v>3.02</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2020</v>
       </c>
@@ -3158,7 +3157,7 @@
         <v>7.19</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>25</v>
       </c>
@@ -3214,7 +3213,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>25</v>
       </c>
@@ -3270,7 +3269,7 @@
         <v>2.84</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="37">
         <v>2019</v>
       </c>
@@ -3324,7 +3323,7 @@
         <v>5.03</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="39">
         <v>2018</v>
       </c>
@@ -3378,7 +3377,7 @@
         <v>5.45</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="37">
         <v>2017</v>
       </c>
@@ -3432,7 +3431,7 @@
         <v>3.71</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="39">
         <v>2016</v>
       </c>
@@ -3486,7 +3485,7 @@
         <v>3.72</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="37">
         <v>2015</v>
       </c>
@@ -3540,7 +3539,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="39">
         <v>2014</v>
       </c>
@@ -3594,7 +3593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="37">
         <v>2013</v>
       </c>
@@ -3648,7 +3647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="39">
         <v>2012</v>
       </c>
@@ -3702,7 +3701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="37">
         <v>2011</v>
       </c>
@@ -3756,7 +3755,7 @@
         <v>2.2599999999999998</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="39">
         <v>2010</v>
       </c>
@@ -3810,7 +3809,7 @@
         <v>3.57</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="37">
         <v>2009</v>
       </c>
@@ -3864,7 +3863,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="39" t="s">
         <v>67</v>
       </c>
